--- a/output/PLAN_PRIORIDADES_MAR_RIO_KIDS.xlsx
+++ b/output/PLAN_PRIORIDADES_MAR_RIO_KIDS.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="RESUMEN" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="INVENTARIO TELA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MAR KIDS CORTADO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MAR KIDS OBJETIVO" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="PRIORIDADES PRODUCCION" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="FLEXIBILIDAD POR COLOR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="METAS EXCEL REF" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,12 +42,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,27 +52,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,18 +87,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,28 +460,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="2" customWidth="1" min="3" max="3"/>
-    <col width="2" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
-    <col width="2" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PLAN DE PRIORIDADES — MAR / RIO (TELA JABÓN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>PLAN PRIORIDADES MAR / RIO — DATOS REALES EXCEL</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fuente metas</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MAR/RIO PROYECCION CANTIDADES SUGERIDAS (2).xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -518,27 +495,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tela usada lote Mar Kids ya cortado (kg)</t>
+          <t>Tela usada lote Mar Kids cortado (kg)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>171.6</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tela neta disponible (kg)</t>
+          <t>Tela neta (kg)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2835</v>
+        <v>2777.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lote Mar Kids cortado (und total)</t>
+          <t>Lote Mar Kids cortado (und)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -548,7 +525,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Und por color en lote (promedio)</t>
+          <t>Und/color lote (~)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -558,158 +535,141 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Objetivo Kids (% pendiente)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
+          <t>Meta máx Mar KIDS (Excel)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3101</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Meta máx Rio KIDS (Excel)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2952</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORDEN DE PRIORIDAD</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Objetivo KIDS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>50% del pendiente (meta − cortado)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Consumo Mar KIDS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.26 kg/und</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Consumo Rio KIDS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.32 kg/und</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ORDEN PRIORIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>MAR KIDS</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>RIO KIDS</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>MAR CAB</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>MAR DAMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>RIO CAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>RIO DAMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>REGLAS DE FLEXIBILIDAD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1. KIDS primero (Mar Kids → Rio Kids) al 50% del pendiente tras descontar lote cortado.</t>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RIO CAB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2. Con tela restante: Mar CAB/DAMA y Rio CAB/DAMA según stock por color.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>3. Colores con &gt;400 kg (Azul Marino, Negro): flexibles entre modelos/géneros.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>4. Rojo (0.18 kg) y Púrpura (0 kg): EXCLUIR de producción.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>5. Si un color no alcanza para un modelo, reasignar a otro modelo del mismo color.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6. Actualizar columnas META con datos reales de los Excel de proyección.</t>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RIO DAMA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A24:F24"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -727,50 +687,50 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Stock kg</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Usado lote Mar Kids</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Disponible neto kg</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Und max KIDS</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Und max CAB</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Und max DAMA</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Neto kg</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Max und Mar KIDS</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Max und Rio KIDS</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Max und Mar CAB</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
@@ -786,23 +746,23 @@
         <v>689.9</v>
       </c>
       <c r="C2" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D2" t="n">
-        <v>674.3</v>
+        <v>659.17</v>
       </c>
       <c r="E2" t="n">
-        <v>5108</v>
+        <v>409</v>
       </c>
       <c r="F2" t="n">
-        <v>3289</v>
+        <v>361</v>
       </c>
       <c r="G2" t="n">
-        <v>3457</v>
+        <v>473</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ALTA — flexibilidad total</t>
+          <t>ALTA flexibilidad</t>
         </is>
       </c>
     </row>
@@ -816,23 +776,23 @@
         <v>657.16</v>
       </c>
       <c r="C3" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D3" t="n">
-        <v>641.5599999999999</v>
+        <v>626.4299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>4860</v>
+        <v>379</v>
       </c>
       <c r="F3" t="n">
-        <v>3129</v>
+        <v>317</v>
       </c>
       <c r="G3" t="n">
-        <v>3290</v>
+        <v>555</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ALTA — flexibilidad total</t>
+          <t>ALTA flexibilidad</t>
         </is>
       </c>
     </row>
@@ -846,21 +806,25 @@
         <v>348.34</v>
       </c>
       <c r="C4" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D4" t="n">
-        <v>332.74</v>
+        <v>317.61</v>
       </c>
       <c r="E4" t="n">
-        <v>2520</v>
+        <v>243</v>
       </c>
       <c r="F4" t="n">
-        <v>1623</v>
+        <v>215</v>
       </c>
       <c r="G4" t="n">
-        <v>1706</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -872,21 +836,25 @@
         <v>271.46</v>
       </c>
       <c r="C5" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D5" t="n">
-        <v>255.86</v>
+        <v>240.73</v>
       </c>
       <c r="E5" t="n">
-        <v>1938</v>
+        <v>232</v>
       </c>
       <c r="F5" t="n">
-        <v>1248</v>
+        <v>284</v>
       </c>
       <c r="G5" t="n">
-        <v>1312</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -898,21 +866,25 @@
         <v>221</v>
       </c>
       <c r="C6" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D6" t="n">
-        <v>205.4</v>
+        <v>190.27</v>
       </c>
       <c r="E6" t="n">
-        <v>1556</v>
+        <v>153</v>
       </c>
       <c r="F6" t="n">
-        <v>1001</v>
+        <v>351</v>
       </c>
       <c r="G6" t="n">
-        <v>1053</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>268</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -924,21 +896,25 @@
         <v>188.44</v>
       </c>
       <c r="C7" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D7" t="n">
-        <v>172.84</v>
+        <v>157.71</v>
       </c>
       <c r="E7" t="n">
-        <v>1309</v>
+        <v>254</v>
       </c>
       <c r="F7" t="n">
-        <v>843</v>
+        <v>294</v>
       </c>
       <c r="G7" t="n">
-        <v>886</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -950,21 +926,25 @@
         <v>175.38</v>
       </c>
       <c r="C8" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D8" t="n">
-        <v>159.78</v>
+        <v>144.65</v>
       </c>
       <c r="E8" t="n">
-        <v>1210</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>819</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>124</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -982,15 +962,19 @@
         <v>162.04</v>
       </c>
       <c r="E9" t="n">
-        <v>1227</v>
+        <v>460</v>
       </c>
       <c r="F9" t="n">
-        <v>790</v>
+        <v>224</v>
       </c>
       <c r="G9" t="n">
-        <v>830</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>390</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1008,15 +992,19 @@
         <v>94.2</v>
       </c>
       <c r="E10" t="n">
-        <v>713</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>459</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>483</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1034,15 +1022,19 @@
         <v>57.94</v>
       </c>
       <c r="E11" t="n">
-        <v>438</v>
+        <v>114</v>
       </c>
       <c r="F11" t="n">
-        <v>282</v>
+        <v>130</v>
       </c>
       <c r="G11" t="n">
-        <v>297</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1054,21 +1046,25 @@
         <v>47.68</v>
       </c>
       <c r="C12" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D12" t="n">
-        <v>32.08</v>
+        <v>16.95</v>
       </c>
       <c r="E12" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>164</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>190</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1080,21 +1076,25 @@
         <v>46.02</v>
       </c>
       <c r="C13" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D13" t="n">
-        <v>30.42</v>
+        <v>15.29</v>
       </c>
       <c r="E13" t="n">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F13" t="n">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="G13" t="n">
-        <v>156</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>355</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1106,23 +1106,23 @@
         <v>31.44</v>
       </c>
       <c r="C14" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D14" t="n">
-        <v>15.84</v>
+        <v>0.71</v>
       </c>
       <c r="E14" t="n">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="F14" t="n">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="G14" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BAJA — solo kids parcial</t>
+          <t>BAJA</t>
         </is>
       </c>
     </row>
@@ -1136,19 +1136,19 @@
         <v>0.18</v>
       </c>
       <c r="C15" t="n">
-        <v>15.6</v>
+        <v>30.73</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1197,360 +1197,419 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Detalle lote Mar Kids ya en corte</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Meta máx Excel</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Ya cortado</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Objetivo 50%</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Und asignar FINAL</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Tela disp kg</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>460</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>460</v>
+      </c>
+      <c r="E2" t="n">
+        <v>230</v>
+      </c>
+      <c r="F2" t="n">
+        <v>230</v>
+      </c>
+      <c r="G2" t="n">
+        <v>162.04</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Talla</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Und lote total</t>
+          <t>Azul Marino</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>409</v>
+      </c>
+      <c r="C3" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>290.8181818181818</v>
+      </c>
+      <c r="E3" t="n">
+        <v>145</v>
+      </c>
+      <c r="F3" t="n">
+        <v>145</v>
+      </c>
+      <c r="G3" t="n">
+        <v>659.17</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Negro</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>260</v>
+        <v>379</v>
+      </c>
+      <c r="C4" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>260.8181818181818</v>
+      </c>
+      <c r="E4" t="n">
+        <v>130</v>
+      </c>
+      <c r="F4" t="n">
+        <v>130</v>
+      </c>
+      <c r="G4" t="n">
+        <v>626.4299999999999</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>260</v>
+        <v>254</v>
+      </c>
+      <c r="C5" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>135.8181818181818</v>
+      </c>
+      <c r="E5" t="n">
+        <v>67</v>
+      </c>
+      <c r="F5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G5" t="n">
+        <v>157.71</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Aguamarina</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>260</v>
+        <v>243</v>
+      </c>
+      <c r="C6" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>124.8181818181818</v>
+      </c>
+      <c r="E6" t="n">
+        <v>62</v>
+      </c>
+      <c r="F6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G6" t="n">
+        <v>317.61</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Rojo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>520</v>
+        <v>239</v>
+      </c>
+      <c r="C7" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>120.8181818181818</v>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SIN TELA</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Azul Rey</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="9"/>
+        <v>232</v>
+      </c>
+      <c r="C8" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>113.8181818181818</v>
+      </c>
+      <c r="E8" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" t="n">
+        <v>56</v>
+      </c>
+      <c r="G8" t="n">
+        <v>240.73</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Verde Militar</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>224</v>
+      </c>
+      <c r="C9" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>105.8181818181818</v>
+      </c>
+      <c r="E9" t="n">
+        <v>52</v>
+      </c>
+      <c r="F9" t="n">
+        <v>52</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Und cortadas (prop.)</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Meta sugerida</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Objetivo 50%</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Tela disp. kg</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rosado Pastel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>214</v>
+      </c>
+      <c r="C10" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>95.81818181818181</v>
+      </c>
+      <c r="E10" t="n">
+        <v>47</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SIN TELA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Verde Militar</t>
+          <t>Púrpura</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>118.2</v>
+        <v>180</v>
       </c>
       <c r="C11" t="n">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2481</v>
+        <v>180</v>
       </c>
       <c r="E11" t="n">
-        <v>1240</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>30.42</v>
+        <v>90</v>
+      </c>
+      <c r="G11" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vinotinto</t>
+          <t>Azul Lavanda</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>153</v>
+      </c>
+      <c r="C12" t="n">
         <v>118.2</v>
       </c>
-      <c r="C12" t="n">
-        <v>2600</v>
-      </c>
       <c r="D12" t="n">
-        <v>2481</v>
+        <v>34.81818181818181</v>
       </c>
       <c r="E12" t="n">
-        <v>1240</v>
+        <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>159.78</v>
+        <v>17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>190.27</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azul Marino</t>
+          <t>Amarillo Neón</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>118.2</v>
+        <v>114</v>
       </c>
       <c r="C13" t="n">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2481</v>
+        <v>114</v>
       </c>
       <c r="E13" t="n">
-        <v>1240</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>674.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Azul Rey</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2481</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F14" t="n">
-        <v>255.86</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Rojo</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2481</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Gris Claro</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2481</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F16" t="n">
-        <v>32.08</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Azul Lavanda</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2481</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F17" t="n">
-        <v>205.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Aguamarina</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2481</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F18" t="n">
-        <v>332.74</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Rosado Pastel</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2481</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F19" t="n">
-        <v>15.84</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Negro</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2481</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F20" t="n">
-        <v>641.5599999999999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Lila</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2481</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1240</v>
-      </c>
-      <c r="F21" t="n">
-        <v>172.84</v>
+        <v>57</v>
+      </c>
+      <c r="G13" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1564,7 +1623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1572,1482 +1631,1576 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Orden</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Modelo</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Género</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Meta sugerida</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Meta máx</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Ya cortado</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>% Objetivo</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>% Obj</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Und objetivo</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>Und asignar FINAL</t>
-        </is>
-      </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Und FINAL</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Kg usar</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
-        <is>
-          <t>Tela restante kg</t>
-        </is>
-      </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Consumo kg/und</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Tela rest kg</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>MAR KIDS</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>KIDS</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Aguamarina</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G2" s="2" t="n">
+      <c r="F2" s="4" t="n">
+        <v>243</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>118.2</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>163.68</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>169.06</v>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="J2" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>301.49</v>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>MAR KIDS</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>KIDS</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Amarillo Neón</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>MAR KIDS</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Azul Lavanda</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G3" s="2" t="n">
+      <c r="F4" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>118.2</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H4" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>163.68</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>41.72</v>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="J4" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>185.85</v>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="P4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>MAR KIDS</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>KIDS</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Azul Marino</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G4" s="2" t="n">
+      <c r="F5" s="4" t="n">
+        <v>409</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>118.2</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H5" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>163.68</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>510.62</v>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="J5" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>621.47</v>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>MAR KIDS</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>KIDS</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Azul Rey</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G5" s="2" t="n">
+      <c r="F6" s="4" t="n">
+        <v>232</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>118.2</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H6" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>163.68</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>92.18000000000001</v>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="J6" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>226.17</v>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="P6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>MAR KIDS</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>KIDS</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Gris Claro</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G6" s="2" t="n">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>460</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>460</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>102.24</v>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>MAR KIDS</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Lila</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>118.2</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H8" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>243</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>32.08</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="J8" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>140.29</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>MAR KIDS</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>592.63</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>MAR KIDS</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Púrpura</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>MAR KIDS</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>SIN TELA</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Stock crítico — excluir o esperar compra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>MAR KIDS</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Rosado Pastel</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>SIN TELA</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Stock crítico — excluir o esperar compra</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>MAR KIDS</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Verde Militar</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Aguamarina</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>267.25</v>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Amarillo Neón</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Azul Lavanda</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>351</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>351</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>129.85</v>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Azul Marino</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>563.87</v>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Azul Rey</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>180.73</v>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Lila</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>47.04</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>317</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>317</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>542.0700000000001</v>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Púrpura</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>SIN TELA</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>Stock crítico — excluir o esperar compra</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Rosado Pastel</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>SIN TELA</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>Stock crítico — excluir o esperar compra</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>RIO KIDS</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Verde Militar</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>MAR KIDS</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Lila</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>163.68</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>9.16</v>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>MAR KIDS</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Negro</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>163.68</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>477.88</v>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>MAR KIDS</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Rojo</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>118.1818181818182</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Stock crítico — excluir o esperar compra</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>MAR KIDS</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Rosado Pastel</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>15.84</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>MAR KIDS</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Verde Militar</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>230</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>30.36</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>MAR KIDS</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Vinotinto</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>2481.818181818182</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>1210</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>159.72</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>RIO KIDS</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Aguamarina</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>23.86</v>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>RIO KIDS</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Azul Lavanda</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>316</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>41.71</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>RIO KIDS</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Azul Marino</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>365.42</v>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>RIO KIDS</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Azul Rey</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>92.14</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>RIO KIDS</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Gris Claro</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>RIO KIDS</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Lila</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>RIO KIDS</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Negro</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>332.68</v>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>RIO KIDS</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Rosado Pastel</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>RIO KIDS</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Verde Militar</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>RIO KIDS</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Vinotinto</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>MAR CAB</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CAB</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Aguamarina</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>800</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>800</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>800</v>
-      </c>
-      <c r="K23" t="n">
-        <v>29</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MAR CAB</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CAB</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Amarillo Neón</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>250</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>250</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>250</v>
-      </c>
-      <c r="K24" t="n">
-        <v>70</v>
-      </c>
-      <c r="L24" t="n">
-        <v>14.35</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>MAR CAB</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CAB</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Azul Lavanda</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>600</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>600</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>600</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>Limitado por tela disponible</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3070,17 +3223,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azul Marino</t>
+          <t>Aguamarina</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1200</v>
+        <v>151</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1200</v>
+        <v>151</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3088,27 +3241,26 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1200</v>
+        <v>151</v>
       </c>
       <c r="K26" t="n">
-        <v>465</v>
+        <v>111</v>
       </c>
       <c r="L26" t="n">
-        <v>95.31999999999999</v>
+        <v>55.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N26" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
-        </is>
-      </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3131,17 +3283,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azul Rey</t>
+          <t>Amarillo Neón</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>700</v>
+        <v>67</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>700</v>
+        <v>67</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3149,23 +3301,26 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>700</v>
+        <v>67</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3188,17 +3343,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Azul Lavanda</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>500</v>
+        <v>268</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>500</v>
+        <v>268</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3206,23 +3361,26 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>500</v>
+        <v>268</v>
       </c>
       <c r="K28" t="n">
-        <v>197</v>
+        <v>67</v>
       </c>
       <c r="L28" t="n">
-        <v>40.38</v>
+        <v>33.5</v>
       </c>
       <c r="M28" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N28" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3245,17 +3403,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gris Claro</t>
+          <t>Azul Marino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>400</v>
+        <v>473</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>400</v>
+        <v>473</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3263,23 +3421,30 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>400</v>
+        <v>473</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>171.5</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3302,17 +3467,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Azul Rey</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>500</v>
+        <v>205</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>500</v>
+        <v>205</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3320,23 +3485,26 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>500</v>
+        <v>205</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3359,17 +3527,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Morado</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3377,23 +3545,30 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="K31" t="n">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="L31" t="n">
-        <v>23.37</v>
+        <v>17</v>
       </c>
       <c r="M31" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N31" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Limitado por tela disponible</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3416,17 +3591,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Negro</t>
+          <t>Gris Claro</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1100</v>
+        <v>190</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1100</v>
+        <v>190</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3434,25 +3609,28 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1100</v>
+        <v>190</v>
       </c>
       <c r="K32" t="n">
-        <v>415</v>
+        <v>19</v>
       </c>
       <c r="L32" t="n">
-        <v>85.06999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="M32" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N32" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Limitado por tela disponible</t>
         </is>
       </c>
     </row>
@@ -3477,17 +3655,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rosado Pastel</t>
+          <t>Negro</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>300</v>
+        <v>555</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>300</v>
+        <v>555</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3495,23 +3673,30 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>300</v>
+        <v>555</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>143.5</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3534,17 +3719,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Verde Militar</t>
+          <t>Rojo</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>400</v>
+        <v>122</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>400</v>
+        <v>122</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3552,7 +3737,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>400</v>
+        <v>122</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3561,14 +3746,21 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N34" s="8" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>SIN TELA</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stock crítico — excluir o esperar compra</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3591,17 +3783,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vinotinto</t>
+          <t>Verde Militar</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>550</v>
+        <v>355</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>550</v>
+        <v>355</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3609,7 +3801,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>550</v>
+        <v>355</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3618,22 +3810,29 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N35" s="8" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>SIN TELA</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Limitado por tela disponible</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MAR DAMA</t>
+          <t>MAR CAB</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3643,22 +3842,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DAMA</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aguamarina</t>
+          <t>Vinotinto</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>900</v>
+        <v>124</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>900</v>
+        <v>124</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3666,23 +3865,26 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>900</v>
+        <v>124</v>
       </c>
       <c r="K36" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="L36" t="n">
-        <v>6.63</v>
+        <v>28</v>
       </c>
       <c r="M36" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N36" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3705,17 +3907,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amarillo Neón</t>
+          <t>Aguamarina</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3723,23 +3925,26 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="K37" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="L37" t="n">
-        <v>16.19</v>
+        <v>49.6</v>
       </c>
       <c r="M37" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N37" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3762,17 +3967,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azul Lavanda</t>
+          <t>Amarillo Neón</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>650</v>
+        <v>67</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>650</v>
+        <v>67</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3780,23 +3985,26 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>650</v>
+        <v>67</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N38" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3819,17 +4027,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azul Marino</t>
+          <t>Azul Lavanda</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1300</v>
+        <v>232</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1300</v>
+        <v>232</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3837,27 +4045,26 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>1300</v>
+        <v>232</v>
       </c>
       <c r="K39" t="n">
-        <v>529</v>
+        <v>72</v>
       </c>
       <c r="L39" t="n">
-        <v>103.16</v>
+        <v>28.8</v>
       </c>
       <c r="M39" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N39" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3880,17 +4087,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azul Rey</t>
+          <t>Azul Marino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>750</v>
+        <v>357</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>750</v>
+        <v>357</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3898,23 +4105,30 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>750</v>
+        <v>357</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>129.2</v>
       </c>
       <c r="M40" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3941,13 +4155,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>550</v>
+        <v>393</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>550</v>
+        <v>393</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3955,23 +4169,26 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>550</v>
+        <v>393</v>
       </c>
       <c r="K41" t="n">
-        <v>228</v>
+        <v>44</v>
       </c>
       <c r="L41" t="n">
-        <v>44.46</v>
+        <v>17.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N41" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3994,17 +4211,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gris Claro</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>450</v>
+        <v>193</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>450</v>
+        <v>193</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4012,23 +4229,26 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>450</v>
+        <v>193</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>37.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4051,17 +4271,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Negro</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>550</v>
+        <v>417</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>550</v>
+        <v>417</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4069,23 +4289,30 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>550</v>
+        <v>417</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M43" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4108,17 +4335,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Morado</t>
+          <t>Púrpura</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>400</v>
+        <v>196</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>400</v>
+        <v>196</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4126,23 +4353,26 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>400</v>
+        <v>196</v>
       </c>
       <c r="K44" t="n">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="L44" t="n">
-        <v>26.91</v>
+        <v>21.2</v>
       </c>
       <c r="M44" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N44" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4165,17 +4395,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Negro</t>
+          <t>Rojo</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1200</v>
+        <v>168</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1200</v>
+        <v>168</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4183,25 +4413,28 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>1200</v>
+        <v>168</v>
       </c>
       <c r="K45" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>92.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
+        <v>0.4</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
+          <t>SIN TELA</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stock crítico — excluir o esperar compra</t>
         </is>
       </c>
     </row>
@@ -4230,13 +4463,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>350</v>
+        <v>108</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>350</v>
+        <v>108</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4244,7 +4477,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>350</v>
+        <v>108</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -4253,14 +4486,21 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="8" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>SIN TELA</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stock crítico — excluir o esperar compra</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4287,13 +4527,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>450</v>
+        <v>272</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>450</v>
+        <v>272</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4301,7 +4541,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>450</v>
+        <v>272</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -4310,14 +4550,21 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N47" s="8" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>SIN TELA</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Limitado por tela disponible</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4344,13 +4591,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>600</v>
+        <v>162</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>600</v>
+        <v>162</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4358,23 +4605,26 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>600</v>
+        <v>162</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>36.8</v>
       </c>
       <c r="M48" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N48" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4401,13 +4651,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>700</v>
+        <v>154</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>700</v>
+        <v>154</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4415,23 +4665,26 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>700</v>
+        <v>154</v>
       </c>
       <c r="K49" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="L49" t="n">
-        <v>5.12</v>
+        <v>56.1</v>
       </c>
       <c r="M49" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N49" t="inlineStr">
+        <v>0.66</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4458,13 +4711,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>220</v>
+        <v>47</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>220</v>
+        <v>47</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4472,23 +4725,26 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>220</v>
+        <v>47</v>
       </c>
       <c r="K50" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="L50" t="n">
-        <v>12.71</v>
+        <v>3.96</v>
       </c>
       <c r="M50" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N50" t="inlineStr">
+        <v>0.66</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="O50" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4515,13 +4771,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>550</v>
+        <v>267</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>550</v>
+        <v>267</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -4529,23 +4785,26 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>550</v>
+        <v>267</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M51" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N51" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
+        <v>0.66</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4572,13 +4831,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1000</v>
+        <v>336</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1000</v>
+        <v>336</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -4586,25 +4845,28 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1000</v>
+        <v>336</v>
       </c>
       <c r="K52" t="n">
-        <v>387</v>
+        <v>184</v>
       </c>
       <c r="L52" t="n">
-        <v>79.33</v>
+        <v>121.44</v>
       </c>
       <c r="M52" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N52" t="inlineStr">
+        <v>0.66</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O52" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
         </is>
       </c>
     </row>
@@ -4633,13 +4895,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>650</v>
+        <v>277</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>650</v>
+        <v>277</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4647,23 +4909,26 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>650</v>
+        <v>277</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>103.62</v>
       </c>
       <c r="M53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N53" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
+        <v>0.66</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4690,13 +4955,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>450</v>
+        <v>356</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>450</v>
+        <v>356</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -4704,23 +4969,30 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>450</v>
+        <v>356</v>
       </c>
       <c r="K54" t="n">
-        <v>177</v>
+        <v>24</v>
       </c>
       <c r="L54" t="n">
-        <v>36.28</v>
+        <v>15.84</v>
       </c>
       <c r="M54" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N54" t="inlineStr">
+        <v>0.66</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O54" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Limitado por tela disponible</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4747,13 +5019,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>350</v>
+        <v>133</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>350</v>
+        <v>133</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4761,23 +5033,30 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>350</v>
+        <v>133</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
+        <v>0.66</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Limitado por tela disponible</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4800,17 +5079,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Negro</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>450</v>
+        <v>557</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>450</v>
+        <v>557</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -4818,23 +5097,30 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>450</v>
+        <v>557</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>143.88</v>
       </c>
       <c r="M56" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N56" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr"/>
+        <v>0.66</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4857,17 +5143,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Morado</t>
+          <t>Rojo</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>300</v>
+        <v>227</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>300</v>
+        <v>227</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4875,23 +5161,30 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>300</v>
+        <v>227</v>
       </c>
       <c r="K57" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>20.09</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
+        <v>0.66</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>SIN TELA</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stock crítico — excluir o esperar compra</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4914,17 +5207,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Negro</t>
+          <t>Verde Militar</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>950</v>
+        <v>245</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>950</v>
+        <v>245</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4932,25 +5225,28 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>950</v>
+        <v>245</v>
       </c>
       <c r="K58" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>73.39</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
+        <v>0.66</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.77</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
+          <t>SIN TELA</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Limitado por tela disponible</t>
         </is>
       </c>
     </row>
@@ -4975,17 +5271,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rosado Pastel</t>
+          <t>Vinotinto</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>280</v>
+        <v>183</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>280</v>
+        <v>183</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4993,31 +5289,34 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>280</v>
+        <v>183</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>41.58</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+        <v>0.66</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RIO CAB</t>
+          <t>RIO DAMA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5027,22 +5326,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>DAMA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Verde Militar</t>
+          <t>Aguamarina</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>350</v>
+        <v>286</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>350</v>
+        <v>286</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5050,31 +5349,34 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>350</v>
+        <v>286</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>105.04</v>
       </c>
       <c r="M60" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N60" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
+        <v>0.52</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RIO CAB</t>
+          <t>RIO DAMA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5084,22 +5386,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>DAMA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vinotinto</t>
+          <t>Amarillo Neón</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>500</v>
+        <v>62</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>500</v>
+        <v>62</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5107,23 +5409,26 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>500</v>
+        <v>62</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M61" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N61" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
+        <v>0.52</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5146,17 +5451,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aguamarina</t>
+          <t>Azul Lavanda</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>800</v>
+        <v>269</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>800</v>
+        <v>269</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5164,23 +5469,26 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>800</v>
+        <v>269</v>
       </c>
       <c r="K62" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="L62" t="n">
-        <v>5.85</v>
+        <v>33.28</v>
       </c>
       <c r="M62" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N62" t="inlineStr">
+        <v>0.52</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O62" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5203,17 +5511,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Amarillo Neón</t>
+          <t>Azul Marino</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>250</v>
+        <v>388</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>250</v>
+        <v>388</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5221,23 +5529,30 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>250</v>
+        <v>388</v>
       </c>
       <c r="K63" t="n">
-        <v>74</v>
+        <v>270</v>
       </c>
       <c r="L63" t="n">
-        <v>14.43</v>
+        <v>140.4</v>
       </c>
       <c r="M63" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N63" t="inlineStr">
+        <v>0.52</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O63" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5260,17 +5575,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azul Lavanda</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>600</v>
+        <v>343</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>600</v>
+        <v>343</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5278,23 +5593,30 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>600</v>
+        <v>343</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>15.08</v>
       </c>
       <c r="M64" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N64" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
+        <v>0.52</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Limitado por tela disponible</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5317,17 +5639,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azul Marino</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1100</v>
+        <v>283</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1100</v>
+        <v>283</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5335,27 +5657,26 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>1100</v>
+        <v>283</v>
       </c>
       <c r="K65" t="n">
-        <v>448</v>
+        <v>106</v>
       </c>
       <c r="L65" t="n">
-        <v>87.36</v>
+        <v>55.12</v>
       </c>
       <c r="M65" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N65" t="inlineStr">
+        <v>0.52</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O65" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
-        </is>
-      </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5378,17 +5699,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azul Rey</t>
+          <t>Negro</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>700</v>
+        <v>561</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>700</v>
+        <v>561</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5396,23 +5717,30 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>700</v>
+        <v>561</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>145.08</v>
       </c>
       <c r="M66" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N66" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
+        <v>0.52</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Alta flexibilidad — repartir entre modelos</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5435,17 +5763,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Púrpura</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5453,23 +5781,26 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="K67" t="n">
-        <v>207</v>
+        <v>29</v>
       </c>
       <c r="L67" t="n">
-        <v>40.37</v>
+        <v>15.08</v>
       </c>
       <c r="M67" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N67" t="inlineStr">
+        <v>0.52</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O67" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5492,17 +5823,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gris Claro</t>
+          <t>Rojo</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5510,7 +5841,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -5519,14 +5850,21 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="8" t="inlineStr">
+        <v>0.52</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="inlineStr">
         <is>
           <t>SIN TELA</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stock crítico — excluir o esperar compra</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5549,17 +5887,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Rosado Pastel</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>500</v>
+        <v>72</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>500</v>
+        <v>72</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5567,7 +5905,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>500</v>
+        <v>72</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -5576,14 +5914,21 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N69" s="8" t="inlineStr">
+        <v>0.52</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O69" t="inlineStr">
         <is>
           <t>SIN TELA</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stock crítico — excluir o esperar compra</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5606,17 +5951,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Morado</t>
+          <t>Verde Militar</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>350</v>
+        <v>146</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>350</v>
+        <v>146</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5624,23 +5969,30 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>350</v>
+        <v>146</v>
       </c>
       <c r="K70" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
+        <v>0.52</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>SIN TELA</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Limitado por tela disponible</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5663,17 +6015,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Negro</t>
+          <t>Vinotinto</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1050</v>
+        <v>163</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1050</v>
+        <v>163</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5681,220 +6033,47 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>1050</v>
+        <v>163</v>
       </c>
       <c r="K71" t="n">
-        <v>416</v>
+        <v>71</v>
       </c>
       <c r="L71" t="n">
-        <v>81.12</v>
+        <v>36.92</v>
       </c>
       <c r="M71" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N71" t="inlineStr">
+        <v>0.52</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O71" t="inlineStr">
         <is>
           <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Alta flexibilidad — puede repartirse entre modelos</t>
-        </is>
-      </c>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>6</v>
-      </c>
+      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RIO DAMA</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>DAMA</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Rosado Pastel</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>320</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>320</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>320</v>
-      </c>
+          <t>TOTALES</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>6124</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>6</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>RIO DAMA</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>DAMA</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Verde Militar</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>400</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>400</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>400</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N73" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>6</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>RIO DAMA</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>DAMA</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Vinotinto</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>550</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>550</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>550</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N74" s="8" t="inlineStr">
-        <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>TOTALES</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="n">
-        <v>18806</v>
-      </c>
-      <c r="L76" t="n">
-        <v>2832.69</v>
+        <v>2670.02</v>
       </c>
     </row>
   </sheetData>
@@ -5908,7 +6087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5919,51 +6098,57 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Tela neta kg</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Mar Kids</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Rio Kids</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Mar KIDS</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Rio KIDS</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Mar CAB</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Mar DAMA</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Rio CAB</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Rio DAMA</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total und</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Recomendación</t>
         </is>
@@ -5976,29 +6161,32 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>674.3</v>
+        <v>659.17</v>
       </c>
       <c r="C2" t="n">
-        <v>1240</v>
+        <v>145</v>
       </c>
       <c r="D2" t="n">
-        <v>1100</v>
+        <v>180</v>
       </c>
       <c r="E2" t="n">
-        <v>465</v>
+        <v>343</v>
       </c>
       <c r="F2" t="n">
-        <v>529</v>
+        <v>323</v>
       </c>
       <c r="G2" t="n">
-        <v>387</v>
+        <v>184</v>
       </c>
       <c r="H2" t="n">
-        <v>448</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Priorizar CAB/DAMA ambos modelos + completar kids</t>
+        <v>270</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Kids 50% + repartir excedente Mar/Rio adultos</t>
         </is>
       </c>
     </row>
@@ -6009,29 +6197,32 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>641.5599999999999</v>
+        <v>626.4299999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1240</v>
+        <v>130</v>
       </c>
       <c r="D3" t="n">
-        <v>1100</v>
+        <v>158</v>
       </c>
       <c r="E3" t="n">
-        <v>415</v>
+        <v>287</v>
       </c>
       <c r="F3" t="n">
-        <v>476</v>
+        <v>270</v>
       </c>
       <c r="G3" t="n">
-        <v>358</v>
+        <v>218</v>
       </c>
       <c r="H3" t="n">
-        <v>416</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Priorizar CAB/DAMA ambos modelos + completar kids</t>
+        <v>279</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1342</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Kids 50% + repartir excedente Mar/Rio adultos</t>
         </is>
       </c>
     </row>
@@ -6042,29 +6233,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>332.74</v>
+        <v>317.61</v>
       </c>
       <c r="C4" t="n">
-        <v>1240</v>
+        <v>62</v>
       </c>
       <c r="D4" t="n">
-        <v>1100</v>
+        <v>107</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Kids 50% + balance CAB/DAMA</t>
+        <v>202</v>
+      </c>
+      <c r="I4" t="n">
+        <v>691</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Kids prioritario + balance adultos</t>
         </is>
       </c>
     </row>
@@ -6075,29 +6269,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>255.86</v>
+        <v>240.73</v>
       </c>
       <c r="C5" t="n">
-        <v>1240</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>698</v>
+        <v>142</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Kids 50% + balance CAB/DAMA</t>
+      <c r="I5" t="n">
+        <v>508</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Kids prioritario + balance adultos</t>
         </is>
       </c>
     </row>
@@ -6108,95 +6305,104 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>205.4</v>
+        <v>190.27</v>
       </c>
       <c r="C6" t="n">
-        <v>1240</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>316</v>
+        <v>175</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Kids 50% + balance CAB/DAMA</t>
+        <v>64</v>
+      </c>
+      <c r="I6" t="n">
+        <v>445</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Kids prioritario + balance adultos</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>172.84</v>
+        <v>162.04</v>
       </c>
       <c r="C7" t="n">
-        <v>1240</v>
+        <v>230</v>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Kids 50% + balance CAB/DAMA</t>
+        <v>29</v>
+      </c>
+      <c r="I7" t="n">
+        <v>473</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Kids prioritario + balance adultos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>162.04</v>
+        <v>157.71</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="E8" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>228</v>
+        <v>94</v>
       </c>
       <c r="G8" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>207</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Kids 50% + balance CAB/DAMA</t>
+        <v>106</v>
+      </c>
+      <c r="I8" t="n">
+        <v>414</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Kids prioritario + balance adultos</t>
         </is>
       </c>
     </row>
@@ -6207,29 +6413,32 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>159.78</v>
+        <v>144.65</v>
       </c>
       <c r="C9" t="n">
-        <v>1210</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Kids 50% + balance CAB/DAMA</t>
+        <v>71</v>
+      </c>
+      <c r="I9" t="n">
+        <v>282</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Kids prioritario + balance adultos</t>
         </is>
       </c>
     </row>
@@ -6249,18 +6458,21 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>120</v>
-      </c>
-      <c r="I10" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Solo KIDS parcial</t>
         </is>
@@ -6269,31 +6481,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Amarillo Neón</t>
+          <t>Púrpura</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57.94</v>
+        <v>94.2</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>74</v>
-      </c>
-      <c r="I11" t="inlineStr">
+        <v>29</v>
+      </c>
+      <c r="I11" t="n">
+        <v>278</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Solo KIDS parcial</t>
         </is>
@@ -6302,31 +6517,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gris Claro</t>
+          <t>Amarillo Neón</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.08</v>
+        <v>57.94</v>
       </c>
       <c r="C12" t="n">
-        <v>243</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>165</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Solo KIDS parcial</t>
         </is>
@@ -6335,31 +6553,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Verde Militar</t>
+          <t>Gris Claro</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.42</v>
+        <v>16.95</v>
       </c>
       <c r="C13" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>29</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Solo KIDS parcial</t>
         </is>
@@ -6368,14 +6589,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rosado Pastel</t>
+          <t>Verde Militar</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.84</v>
+        <v>15.29</v>
       </c>
       <c r="C14" t="n">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -6392,7 +6613,10 @@
       <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>52</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Solo KIDS parcial</t>
         </is>
@@ -6401,11 +6625,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Púrpura</t>
+          <t>Rosado Pastel</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -6425,9 +6649,12 @@
       <c r="H15" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>No producir — sin tela</t>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NO PRODUCIR — sin tela</t>
         </is>
       </c>
     </row>
@@ -6458,10 +6685,1455 @@
       <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>No producir — sin tela</t>
-        </is>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NO PRODUCIR — sin tela</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Género</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Máximo sugerido</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Azul Marino</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Lila</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Aguamarina</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Azul Rey</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Verde Militar</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rosado Pastel</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Púrpura</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Azul Lavanda</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amarillo Neón</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Azul Marino</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Verde Militar</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Azul Lavanda</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Azul Rey</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Gris Claro</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Aguamarina</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Vinotinto</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Amarillo Neón</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Azul Marino</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Verde Militar</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Azul Lavanda</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Púrpura</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lila</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Vinotinto</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Aguamarina</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Rosado Pastel</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Amarillo Neón</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Azul Marino</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Azul Lavanda</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Lila</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Azul Rey</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Aguamarina</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Púrpura</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Verde Militar</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Rosado Pastel</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>KIDS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Amarillo Neón</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Azul Marino</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Azul Rey</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Azul Lavanda</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Verde Militar</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Vinotinto</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Aguamarina</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Gris Claro</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Amarillo Neón</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Azul Marino</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Aguamarina</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Lila</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Azul Lavanda</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Vinotinto</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Verde Militar</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Púrpura</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Rosado Pastel</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>DAMA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Amarillo Neón</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/output/PLAN_PRIORIDADES_MAR_RIO_KIDS.xlsx
+++ b/output/PLAN_PRIORIDADES_MAR_RIO_KIDS.xlsx
@@ -495,41 +495,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tela usada lote Mar Kids cortado (kg)</t>
+          <t>Inventario tela actual (kg) — foto</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>338</v>
+        <v>2991.18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tela neta (kg)</t>
+          <t>Lote Mar Kids cortado (und) — tela de PRODUCCIÓN, no inventario</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2777.93</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lote Mar Kids cortado (und)</t>
+          <t>Und/color lote (~118 und, rep. proporcional)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1300</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Und/color lote (~)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>118.2</v>
+          <t>Nota lote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Solo descuenta UND de meta Mar KIDS; NO resta kg del inventario</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -681,17 +683,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -702,35 +703,30 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Stock kg</t>
+          <t>Inventario kg (foto)</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Usado lote Mar Kids</t>
+          <t>Und ya cortadas Mar KIDS</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Neto kg</t>
+          <t>Max und Mar KIDS Excel</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Max und Mar KIDS</t>
+          <t>Max und Rio KIDS</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Max und Rio KIDS</t>
+          <t>Max und Mar CAB</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Max und Mar CAB</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
@@ -746,21 +742,18 @@
         <v>689.9</v>
       </c>
       <c r="C2" t="n">
-        <v>30.73</v>
+        <v>118.2</v>
       </c>
       <c r="D2" t="n">
-        <v>659.17</v>
+        <v>409</v>
       </c>
       <c r="E2" t="n">
-        <v>409</v>
+        <v>361</v>
       </c>
       <c r="F2" t="n">
-        <v>361</v>
-      </c>
-      <c r="G2" t="n">
         <v>473</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ALTA flexibilidad</t>
         </is>
@@ -776,21 +769,18 @@
         <v>657.16</v>
       </c>
       <c r="C3" t="n">
-        <v>30.73</v>
+        <v>118.2</v>
       </c>
       <c r="D3" t="n">
-        <v>626.4299999999999</v>
+        <v>379</v>
       </c>
       <c r="E3" t="n">
-        <v>379</v>
+        <v>317</v>
       </c>
       <c r="F3" t="n">
-        <v>317</v>
-      </c>
-      <c r="G3" t="n">
         <v>555</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>ALTA flexibilidad</t>
         </is>
@@ -806,21 +796,18 @@
         <v>348.34</v>
       </c>
       <c r="C4" t="n">
-        <v>30.73</v>
+        <v>118.2</v>
       </c>
       <c r="D4" t="n">
-        <v>317.61</v>
+        <v>243</v>
       </c>
       <c r="E4" t="n">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="F4" t="n">
-        <v>215</v>
-      </c>
-      <c r="G4" t="n">
         <v>151</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -836,21 +823,18 @@
         <v>271.46</v>
       </c>
       <c r="C5" t="n">
-        <v>30.73</v>
+        <v>118.2</v>
       </c>
       <c r="D5" t="n">
-        <v>240.73</v>
+        <v>232</v>
       </c>
       <c r="E5" t="n">
-        <v>232</v>
+        <v>284</v>
       </c>
       <c r="F5" t="n">
-        <v>284</v>
-      </c>
-      <c r="G5" t="n">
         <v>205</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -866,21 +850,18 @@
         <v>221</v>
       </c>
       <c r="C6" t="n">
-        <v>30.73</v>
+        <v>118.2</v>
       </c>
       <c r="D6" t="n">
-        <v>190.27</v>
+        <v>153</v>
       </c>
       <c r="E6" t="n">
-        <v>153</v>
+        <v>351</v>
       </c>
       <c r="F6" t="n">
-        <v>351</v>
-      </c>
-      <c r="G6" t="n">
         <v>268</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -896,21 +877,18 @@
         <v>188.44</v>
       </c>
       <c r="C7" t="n">
-        <v>30.73</v>
+        <v>118.2</v>
       </c>
       <c r="D7" t="n">
-        <v>157.71</v>
+        <v>254</v>
       </c>
       <c r="E7" t="n">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="F7" t="n">
-        <v>294</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -926,21 +904,18 @@
         <v>175.38</v>
       </c>
       <c r="C8" t="n">
-        <v>30.73</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>144.65</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
         <v>124</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -959,18 +934,15 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>162.04</v>
+        <v>460</v>
       </c>
       <c r="E9" t="n">
-        <v>460</v>
+        <v>224</v>
       </c>
       <c r="F9" t="n">
-        <v>224</v>
-      </c>
-      <c r="G9" t="n">
         <v>390</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -989,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>94.2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -997,10 +969,7 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -1019,18 +988,15 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>57.94</v>
+        <v>114</v>
       </c>
       <c r="E11" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="F11" t="n">
-        <v>130</v>
-      </c>
-      <c r="G11" t="n">
         <v>67</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -1046,23 +1012,20 @@
         <v>47.68</v>
       </c>
       <c r="C12" t="n">
-        <v>30.73</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>16.95</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
         <v>190</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>BAJA</t>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
     </row>
@@ -1076,23 +1039,20 @@
         <v>46.02</v>
       </c>
       <c r="C13" t="n">
-        <v>30.73</v>
+        <v>118.2</v>
       </c>
       <c r="D13" t="n">
-        <v>15.29</v>
+        <v>224</v>
       </c>
       <c r="E13" t="n">
-        <v>224</v>
+        <v>162</v>
       </c>
       <c r="F13" t="n">
-        <v>162</v>
-      </c>
-      <c r="G13" t="n">
         <v>355</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>BAJA</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
     </row>
@@ -1106,23 +1066,20 @@
         <v>31.44</v>
       </c>
       <c r="C14" t="n">
-        <v>30.73</v>
+        <v>118.2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.71</v>
+        <v>214</v>
       </c>
       <c r="E14" t="n">
-        <v>214</v>
+        <v>142</v>
       </c>
       <c r="F14" t="n">
-        <v>142</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>BAJA</t>
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
     </row>
@@ -1136,51 +1093,18 @@
         <v>0.18</v>
       </c>
       <c r="C15" t="n">
-        <v>30.73</v>
+        <v>118.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="E15" t="n">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="F15" t="n">
-        <v>260</v>
-      </c>
-      <c r="G15" t="n">
         <v>122</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>SIN STOCK</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Púrpura</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>180</v>
-      </c>
-      <c r="F16" t="n">
-        <v>212</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>SIN STOCK</t>
         </is>
@@ -1304,7 +1228,7 @@
         <v>145</v>
       </c>
       <c r="G3" t="n">
-        <v>659.17</v>
+        <v>689.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1334,7 +1258,7 @@
         <v>130</v>
       </c>
       <c r="G4" t="n">
-        <v>626.4299999999999</v>
+        <v>657.16</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1364,7 +1288,7 @@
         <v>67</v>
       </c>
       <c r="G5" t="n">
-        <v>157.71</v>
+        <v>188.44</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1394,7 +1318,7 @@
         <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>317.61</v>
+        <v>348.34</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1424,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1454,7 +1378,7 @@
         <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>240.73</v>
+        <v>271.46</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1484,7 +1408,7 @@
         <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>15.29</v>
+        <v>46.02</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1511,14 +1435,14 @@
         <v>47</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>0.71</v>
+        <v>31.44</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SIN TELA</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1498,7 @@
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>190.27</v>
+        <v>221</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1777,7 +1701,7 @@
         <v>0.26</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>301.49</v>
+        <v>332.22</v>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
@@ -1897,7 +1821,7 @@
         <v>0.26</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>185.85</v>
+        <v>216.58</v>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
@@ -1957,7 +1881,7 @@
         <v>0.26</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>621.47</v>
+        <v>652.2</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
@@ -2021,7 +1945,7 @@
         <v>0.26</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>226.17</v>
+        <v>256.9</v>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
@@ -2141,7 +2065,7 @@
         <v>0.26</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>140.29</v>
+        <v>171.02</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
@@ -2201,7 +2125,7 @@
         <v>0.26</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>592.63</v>
+        <v>623.36</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -2325,7 +2249,7 @@
         <v>0.26</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -2380,27 +2304,23 @@
         <v>47</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>12.22</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>0.26</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.71</v>
+        <v>19.22</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>Stock crítico — excluir o esperar compra</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -2453,7 +2373,7 @@
         <v>0.26</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.77</v>
+        <v>32.5</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -2513,7 +2433,7 @@
         <v>0.32</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>267.25</v>
+        <v>297.98</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
@@ -2633,7 +2553,7 @@
         <v>0.32</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>129.85</v>
+        <v>160.58</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
@@ -2693,7 +2613,7 @@
         <v>0.32</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>563.87</v>
+        <v>594.6</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
@@ -2757,7 +2677,7 @@
         <v>0.32</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>180.73</v>
+        <v>211.46</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
@@ -2877,7 +2797,7 @@
         <v>0.32</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>93.25</v>
+        <v>123.98</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
@@ -2937,7 +2857,7 @@
         <v>0.32</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>542.0700000000001</v>
+        <v>572.8</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
@@ -3061,7 +2981,7 @@
         <v>0.32</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -3116,27 +3036,23 @@
         <v>71</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="M24" s="4" t="n">
         <v>0.32</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.71</v>
+        <v>0.02</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>SIN TELA</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="inlineStr">
-        <is>
-          <t>Stock crítico — excluir o esperar compra</t>
-        </is>
-      </c>
+          <t>PARCIAL (limitado tela)</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -3180,27 +3096,23 @@
         <v>81</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0</v>
+        <v>25.92</v>
       </c>
       <c r="M25" s="4" t="n">
         <v>0.32</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.77</v>
+        <v>6.58</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>PARCIAL (limitado tela)</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>Limitado por tela disponible</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3244,16 +3156,16 @@
         <v>151</v>
       </c>
       <c r="K26" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="L26" t="n">
-        <v>55.5</v>
+        <v>61.5</v>
       </c>
       <c r="M26" t="n">
         <v>0.5</v>
       </c>
       <c r="N26" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -3364,16 +3276,16 @@
         <v>268</v>
       </c>
       <c r="K28" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="L28" t="n">
-        <v>33.5</v>
+        <v>41.5</v>
       </c>
       <c r="M28" t="n">
         <v>0.5</v>
       </c>
       <c r="N28" t="n">
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -3424,16 +3336,16 @@
         <v>473</v>
       </c>
       <c r="K29" t="n">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="L29" t="n">
-        <v>171.5</v>
+        <v>180.5</v>
       </c>
       <c r="M29" t="n">
         <v>0.5</v>
       </c>
       <c r="N29" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3488,16 +3400,16 @@
         <v>205</v>
       </c>
       <c r="K30" t="n">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="L30" t="n">
-        <v>76.5</v>
+        <v>89.5</v>
       </c>
       <c r="M30" t="n">
         <v>0.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -3612,16 +3524,16 @@
         <v>190</v>
       </c>
       <c r="K32" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="L32" t="n">
-        <v>9.5</v>
+        <v>28</v>
       </c>
       <c r="M32" t="n">
         <v>0.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0.85</v>
+        <v>0.54</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3676,16 +3588,16 @@
         <v>555</v>
       </c>
       <c r="K33" t="n">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="L33" t="n">
-        <v>143.5</v>
+        <v>152</v>
       </c>
       <c r="M33" t="n">
         <v>0.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1.61</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3749,7 +3661,7 @@
         <v>0.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3804,20 +3716,20 @@
         <v>355</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
         <v>0.5</v>
       </c>
       <c r="N35" t="n">
-        <v>1.77</v>
+        <v>1.14</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>SIN TELA</t>
+          <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3868,16 +3780,16 @@
         <v>124</v>
       </c>
       <c r="K36" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="L36" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M36" t="n">
         <v>0.5</v>
       </c>
       <c r="N36" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3928,20 +3840,20 @@
         <v>135</v>
       </c>
       <c r="K37" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L37" t="n">
-        <v>49.6</v>
+        <v>54</v>
       </c>
       <c r="M37" t="n">
         <v>0.4</v>
       </c>
       <c r="N37" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>PARCIAL (limitado tela)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -4048,16 +3960,16 @@
         <v>232</v>
       </c>
       <c r="K39" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="L39" t="n">
-        <v>28.8</v>
+        <v>35.6</v>
       </c>
       <c r="M39" t="n">
         <v>0.4</v>
       </c>
       <c r="N39" t="n">
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4108,16 +4020,16 @@
         <v>357</v>
       </c>
       <c r="K40" t="n">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L40" t="n">
-        <v>129.2</v>
+        <v>136.4</v>
       </c>
       <c r="M40" t="n">
         <v>0.4</v>
       </c>
       <c r="N40" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -4232,16 +4144,16 @@
         <v>193</v>
       </c>
       <c r="K42" t="n">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="L42" t="n">
-        <v>37.6</v>
+        <v>50</v>
       </c>
       <c r="M42" t="n">
         <v>0.4</v>
       </c>
       <c r="N42" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4292,16 +4204,16 @@
         <v>417</v>
       </c>
       <c r="K43" t="n">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L43" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="M43" t="n">
         <v>0.4</v>
       </c>
       <c r="N43" t="n">
-        <v>1.61</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4425,7 +4337,7 @@
         <v>0.4</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4489,7 +4401,7 @@
         <v>0.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0.71</v>
+        <v>0.02</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4498,7 +4410,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stock crítico — excluir o esperar compra</t>
+          <t>Limitado por tela disponible</t>
         </is>
       </c>
     </row>
@@ -4544,20 +4456,20 @@
         <v>272</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M47" t="n">
         <v>0.4</v>
       </c>
       <c r="N47" t="n">
-        <v>1.77</v>
+        <v>1.14</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>SIN TELA</t>
+          <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4608,16 +4520,16 @@
         <v>162</v>
       </c>
       <c r="K48" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="L48" t="n">
-        <v>36.8</v>
+        <v>44.8</v>
       </c>
       <c r="M48" t="n">
         <v>0.4</v>
       </c>
       <c r="N48" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4668,16 +4580,16 @@
         <v>154</v>
       </c>
       <c r="K49" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L49" t="n">
-        <v>56.1</v>
+        <v>62.7</v>
       </c>
       <c r="M49" t="n">
         <v>0.66</v>
       </c>
       <c r="N49" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4788,16 +4700,16 @@
         <v>267</v>
       </c>
       <c r="K51" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="L51" t="n">
-        <v>33</v>
+        <v>40.92</v>
       </c>
       <c r="M51" t="n">
         <v>0.66</v>
       </c>
       <c r="N51" t="n">
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4848,16 +4760,16 @@
         <v>336</v>
       </c>
       <c r="K52" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="L52" t="n">
-        <v>121.44</v>
+        <v>128.04</v>
       </c>
       <c r="M52" t="n">
         <v>0.66</v>
       </c>
       <c r="N52" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4912,16 +4824,16 @@
         <v>277</v>
       </c>
       <c r="K53" t="n">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="L53" t="n">
-        <v>103.62</v>
+        <v>121.44</v>
       </c>
       <c r="M53" t="n">
         <v>0.66</v>
       </c>
       <c r="N53" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -5036,16 +4948,16 @@
         <v>133</v>
       </c>
       <c r="K55" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="L55" t="n">
-        <v>6.6</v>
+        <v>19.14</v>
       </c>
       <c r="M55" t="n">
         <v>0.66</v>
       </c>
       <c r="N55" t="n">
-        <v>0.85</v>
+        <v>0.54</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5100,16 +5012,16 @@
         <v>557</v>
       </c>
       <c r="K56" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="L56" t="n">
-        <v>143.88</v>
+        <v>152.46</v>
       </c>
       <c r="M56" t="n">
         <v>0.66</v>
       </c>
       <c r="N56" t="n">
-        <v>1.61</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5173,7 +5085,7 @@
         <v>0.66</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5228,20 +5140,20 @@
         <v>245</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M58" t="n">
         <v>0.66</v>
       </c>
       <c r="N58" t="n">
-        <v>1.77</v>
+        <v>1.14</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>SIN TELA</t>
+          <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5292,16 +5204,16 @@
         <v>183</v>
       </c>
       <c r="K59" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="L59" t="n">
-        <v>41.58</v>
+        <v>50.16</v>
       </c>
       <c r="M59" t="n">
         <v>0.66</v>
       </c>
       <c r="N59" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5352,16 +5264,16 @@
         <v>286</v>
       </c>
       <c r="K60" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="L60" t="n">
-        <v>105.04</v>
+        <v>117</v>
       </c>
       <c r="M60" t="n">
         <v>0.52</v>
       </c>
       <c r="N60" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5472,16 +5384,16 @@
         <v>269</v>
       </c>
       <c r="K62" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="L62" t="n">
-        <v>33.28</v>
+        <v>41.6</v>
       </c>
       <c r="M62" t="n">
         <v>0.52</v>
       </c>
       <c r="N62" t="n">
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5532,16 +5444,16 @@
         <v>388</v>
       </c>
       <c r="K63" t="n">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="L63" t="n">
-        <v>140.4</v>
+        <v>148.2</v>
       </c>
       <c r="M63" t="n">
         <v>0.52</v>
       </c>
       <c r="N63" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5660,16 +5572,16 @@
         <v>283</v>
       </c>
       <c r="K65" t="n">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L65" t="n">
-        <v>55.12</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="M65" t="n">
         <v>0.52</v>
       </c>
       <c r="N65" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5720,16 +5632,16 @@
         <v>561</v>
       </c>
       <c r="K66" t="n">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="L66" t="n">
-        <v>145.08</v>
+        <v>153.4</v>
       </c>
       <c r="M66" t="n">
         <v>0.52</v>
       </c>
       <c r="N66" t="n">
-        <v>1.61</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -5853,7 +5765,7 @@
         <v>0.52</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -5917,7 +5829,7 @@
         <v>0.52</v>
       </c>
       <c r="N69" t="n">
-        <v>0.71</v>
+        <v>0.02</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -5926,7 +5838,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stock crítico — excluir o esperar compra</t>
+          <t>Limitado por tela disponible</t>
         </is>
       </c>
     </row>
@@ -5972,20 +5884,20 @@
         <v>146</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M70" t="n">
         <v>0.52</v>
       </c>
       <c r="N70" t="n">
-        <v>1.77</v>
+        <v>1.14</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>SIN TELA</t>
+          <t>PARCIAL (limitado tela)</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6036,16 +5948,16 @@
         <v>163</v>
       </c>
       <c r="K71" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="L71" t="n">
-        <v>36.92</v>
+        <v>44.72</v>
       </c>
       <c r="M71" t="n">
         <v>0.52</v>
       </c>
       <c r="N71" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6070,10 +5982,10 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
-        <v>6124</v>
+        <v>6797</v>
       </c>
       <c r="L72" t="n">
-        <v>2670.02</v>
+        <v>2977.64</v>
       </c>
     </row>
   </sheetData>
@@ -6161,7 +6073,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>659.17</v>
+        <v>689.9</v>
       </c>
       <c r="C2" t="n">
         <v>145</v>
@@ -6170,19 +6082,19 @@
         <v>180</v>
       </c>
       <c r="E2" t="n">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="F2" t="n">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="G2" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H2" t="n">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="I2" t="n">
-        <v>1445</v>
+        <v>1506</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -6197,7 +6109,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>626.4299999999999</v>
+        <v>657.16</v>
       </c>
       <c r="C3" t="n">
         <v>130</v>
@@ -6206,19 +6118,19 @@
         <v>158</v>
       </c>
       <c r="E3" t="n">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="F3" t="n">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="G3" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="H3" t="n">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="I3" t="n">
-        <v>1342</v>
+        <v>1403</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -6233,7 +6145,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>317.61</v>
+        <v>348.34</v>
       </c>
       <c r="C4" t="n">
         <v>62</v>
@@ -6242,19 +6154,19 @@
         <v>107</v>
       </c>
       <c r="E4" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H4" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="I4" t="n">
-        <v>691</v>
+        <v>747</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -6269,7 +6181,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>240.73</v>
+        <v>271.46</v>
       </c>
       <c r="C5" t="n">
         <v>56</v>
@@ -6278,19 +6190,19 @@
         <v>142</v>
       </c>
       <c r="E5" t="n">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>508</v>
+        <v>561</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -6305,7 +6217,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>190.27</v>
+        <v>221</v>
       </c>
       <c r="C6" t="n">
         <v>17</v>
@@ -6314,19 +6226,19 @@
         <v>175</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H6" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="I6" t="n">
-        <v>445</v>
+        <v>506</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -6337,32 +6249,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>162.04</v>
+        <v>188.44</v>
       </c>
       <c r="C7" t="n">
-        <v>230</v>
+        <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="I7" t="n">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -6373,32 +6285,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Vinotinto</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>157.71</v>
+        <v>175.38</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="I8" t="n">
-        <v>414</v>
+        <v>342</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -6409,32 +6321,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vinotinto</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>144.65</v>
+        <v>162.04</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="H9" t="n">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="I9" t="n">
-        <v>282</v>
+        <v>473</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -6445,32 +6357,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Morado</t>
+          <t>Púrpura</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>94.2</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -6481,32 +6393,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Púrpura</t>
+          <t>Morado</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>94.2</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -6557,7 +6469,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.95</v>
+        <v>47.68</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -6566,19 +6478,19 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -6593,28 +6505,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.29</v>
+        <v>46.02</v>
       </c>
       <c r="C14" t="n">
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -6629,13 +6541,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.71</v>
+        <v>31.44</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6650,11 +6562,11 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>NO PRODUCIR — sin tela</t>
+          <t>Solo KIDS parcial</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6577,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
